--- a/sample_data/tests/03 - Datasheet for losses calculation.xlsx
+++ b/sample_data/tests/03 - Datasheet for losses calculation.xlsx
@@ -7,13 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Losses datasheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Loss Measurement Datasheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="LS_SERIES">'Losses datasheet'!$B$3</definedName>
-    <definedName name="LS_SAMPLE">'Losses datasheet'!$E$3</definedName>
-    <definedName name="LS_NLL_BT">'Losses datasheet'!$B$4</definedName>
-    <definedName name="LS_NLL_AT">'Losses datasheet'!$E$4</definedName>
+    <definedName name="LS2_SERIES">'Loss Measurement Datasheet'!$E$6</definedName>
+    <definedName name="LS2_SAMPLE">'Loss Measurement Datasheet'!$M$6</definedName>
+    <definedName name="LS2_SAMPLE_DETAILS">'Loss Measurement Datasheet'!$F$7</definedName>
+    <definedName name="LS2_EEL_LIMITS">'Loss Measurement Datasheet'!$F$8</definedName>
+    <definedName name="LS2_SIG_ENGINEER">'Loss Measurement Datasheet'!$A$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,24 +32,54 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <sz val="13"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="6"/>
     </font>
     <font>
       <i val="1"/>
-      <color rgb="0056667F"/>
+      <color rgb="001C3D6E"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF3FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF1F5"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -61,7 +92,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -83,22 +114,95 @@
         <color rgb="009AA8BD"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="009AA8BD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="009AA8BD"/>
+      </right>
+      <top style="thin">
+        <color rgb="009AA8BD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="009AA8BD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009AA8BD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="009AA8BD"/>
+      </right>
+      <top style="thin">
+        <color rgb="009AA8BD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009AA8BD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -463,445 +567,1096 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="9.5" customWidth="1" min="1" max="1"/>
+    <col width="9.5" customWidth="1" min="2" max="2"/>
+    <col width="9.5" customWidth="1" min="3" max="3"/>
+    <col width="9.5" customWidth="1" min="4" max="4"/>
+    <col width="9.5" customWidth="1" min="5" max="5"/>
+    <col width="9.5" customWidth="1" min="6" max="6"/>
+    <col width="9.5" customWidth="1" min="7" max="7"/>
+    <col width="9.5" customWidth="1" min="8" max="8"/>
+    <col width="9.5" customWidth="1" min="9" max="9"/>
+    <col width="9.5" customWidth="1" min="10" max="10"/>
+    <col width="9.5" customWidth="1" min="11" max="11"/>
+    <col width="9.5" customWidth="1" min="12" max="12"/>
+    <col width="9.5" customWidth="1" min="13" max="13"/>
+    <col width="9.5" customWidth="1" min="14" max="14"/>
+    <col width="9.5" customWidth="1" min="15" max="15"/>
+    <col width="9.5" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" hidden="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Losses datasheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+          <t>Aletheia template losses v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CPRI Short Circuit Laboratory - form: Aletheia template losses (version 1). Fill the yellow cells only; do not move or rename them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>Fill in the yellow cells as on the paper logsheet. Grey cells are printed text or are calculated; they are locked. Choose from the list where a cell offers one; readings must be numbers and dates must be dates (dd-mm-yyyy). Leave a cell empty if the value is not on the sheet: it is recorded as NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Test series no. (as written)</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+          <t>SHORT CIRCUIT LABORATORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>CPRI SCL Transformer Loss Measurement v2.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Series No :</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>CPRIBLRSCL25T1654</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Sample code no. (as written)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="10" t="n"/>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Sample No :</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="7" t="n"/>
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t>HVD25S0847</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>No-load loss before SC (W)</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
+      <c r="N6" s="9" t="n"/>
+      <c r="O6" s="9" t="n"/>
+      <c r="P6" s="10" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Sample Details :</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="9" t="n"/>
+      <c r="I7" s="9" t="n"/>
+      <c r="J7" s="9" t="n"/>
+      <c r="K7" s="9" t="n"/>
+      <c r="L7" s="9" t="n"/>
+      <c r="M7" s="9" t="n"/>
+      <c r="N7" s="9" t="n"/>
+      <c r="O7" s="9" t="n"/>
+      <c r="P7" s="10" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>EEL limits</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="9" t="n"/>
+      <c r="I8" s="9" t="n"/>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="9" t="n"/>
+      <c r="L8" s="9" t="n"/>
+      <c r="M8" s="9" t="n"/>
+      <c r="N8" s="9" t="n"/>
+      <c r="O8" s="9" t="n"/>
+      <c r="P8" s="10" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>No Load Loss</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="7" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>No Load Loss</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>BT</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n">
         <v>383.18</v>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>No-load loss after SC (W)</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="n">
+      <c r="E11" s="14" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n">
         <v>383.26</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Losses and impedance (75 C)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Tap / condition</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>%Z</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>%X</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>%X change</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>R HV (ohm)</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>R LV (mohm)</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>Load loss 100% (W)</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>X/R</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>Isc peak (kA)</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>Isc rms (kA)</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>Stray loss (W)</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>Load loss 50% (W)</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>Total loss 50% (W)</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>Total loss 100% (W)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="E12" s="14" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>50% Load Loss</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>V (50%)</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>I (50%)</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>P (50%)</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>f (50%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="n"/>
+      <c r="B16" s="14" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>LV Resistance (milliOhm)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="7" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>LV Resistance</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>LVR1</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>LVR2</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>LVR3</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>Temp</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>BT</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="14" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="14" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Load Loss Measurement</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Load Loss</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>I1</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>I2</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>I3</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J24" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K24" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f </t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>NTBT</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B25" s="14" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="14" t="n"/>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="14" t="n"/>
+      <c r="H25" s="14" t="n"/>
+      <c r="I25" s="14" t="n"/>
+      <c r="J25" s="14" t="n"/>
+      <c r="K25" s="14" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>NTAT</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="n"/>
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="14" t="n"/>
+      <c r="E26" s="14" t="n"/>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="14" t="n"/>
+      <c r="H26" s="14" t="n"/>
+      <c r="I26" s="14" t="n"/>
+      <c r="J26" s="14" t="n"/>
+      <c r="K26" s="14" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>HTBT</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="n"/>
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="14" t="n"/>
+      <c r="E27" s="14" t="n"/>
+      <c r="F27" s="14" t="n"/>
+      <c r="G27" s="14" t="n"/>
+      <c r="H27" s="14" t="n"/>
+      <c r="I27" s="14" t="n"/>
+      <c r="J27" s="14" t="n"/>
+      <c r="K27" s="14" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>HTAT</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="n"/>
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="14" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="14" t="n"/>
+      <c r="H28" s="14" t="n"/>
+      <c r="I28" s="14" t="n"/>
+      <c r="J28" s="14" t="n"/>
+      <c r="K28" s="14" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>LTBT</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="14" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="14" t="n"/>
+      <c r="H29" s="14" t="n"/>
+      <c r="I29" s="14" t="n"/>
+      <c r="J29" s="14" t="n"/>
+      <c r="K29" s="14" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>LTAT</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="14" t="n"/>
+      <c r="H30" s="14" t="n"/>
+      <c r="I30" s="14" t="n"/>
+      <c r="J30" s="14" t="n"/>
+      <c r="K30" s="14" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>HV Resistance (Ohm)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="7" t="n"/>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>HV Resistance</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>HVR1</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>HVR2</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>HVR3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>NTBT</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="n"/>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="14" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>NTAT</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="n"/>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="14" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>HTBT</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>HTAT</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>LTBT</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="14" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>LTAT</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="14" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>Load Loss Results (Ref Temp : 75 degC)</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="6" t="n"/>
+      <c r="G41" s="6" t="n"/>
+      <c r="H41" s="6" t="n"/>
+      <c r="I41" s="6" t="n"/>
+      <c r="J41" s="6" t="n"/>
+      <c r="K41" s="6" t="n"/>
+      <c r="L41" s="6" t="n"/>
+      <c r="M41" s="6" t="n"/>
+      <c r="N41" s="7" t="n"/>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Tap</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>%Z-75deg</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>%X-50Hz</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>%X Change</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>Rhv-Ohm</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>Rlv-mOhm</t>
+        </is>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>100% LoadLoss</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>X/R-75deg</t>
+        </is>
+      </c>
+      <c r="I42" s="12" t="inlineStr">
+        <is>
+          <t>Isc-pk</t>
+        </is>
+      </c>
+      <c r="J42" s="12" t="inlineStr">
+        <is>
+          <t>Isc-rms</t>
+        </is>
+      </c>
+      <c r="K42" s="12" t="inlineStr">
+        <is>
+          <t>Stray Loss</t>
+        </is>
+      </c>
+      <c r="L42" s="12" t="inlineStr">
+        <is>
+          <t>50% LoadLoss</t>
+        </is>
+      </c>
+      <c r="M42" s="12" t="inlineStr">
+        <is>
+          <t>50% TotalLoss</t>
+        </is>
+      </c>
+      <c r="N42" s="12" t="inlineStr">
+        <is>
+          <t>100% TotalLoss</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>NTBT</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="n">
         <v>4.38</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C43" s="14" t="n">
         <v>4.299</v>
       </c>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n">
+      <c r="D43" s="14" t="n"/>
+      <c r="E43" s="14" t="n">
         <v>7.101</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F43" s="14" t="n">
         <v>2.317</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G43" s="14" t="n">
         <v>2102.74</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H43" s="14" t="n">
         <v>5.112</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I43" s="14" t="n">
         <v>16.73</v>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="J43" s="14" t="n">
         <v>7.61</v>
       </c>
-      <c r="K9" s="5" t="n">
+      <c r="K43" s="14" t="n">
         <v>107.62</v>
       </c>
-      <c r="L9" s="5" t="n">
+      <c r="L43" s="14" t="n">
         <v>524.91</v>
       </c>
-      <c r="M9" s="5" t="n">
+      <c r="M43" s="14" t="n">
         <v>908.09</v>
       </c>
-      <c r="N9" s="5" t="n">
+      <c r="N43" s="14" t="n">
         <v>2485.92</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
         <is>
           <t>NTAT</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B44" s="14" t="n">
         <v>4.387</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C44" s="14" t="n">
         <v>4.306</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D44" s="14" t="n">
         <v>-0.163</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E44" s="14" t="n">
         <v>7.098</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F44" s="14" t="n">
         <v>2.318</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G44" s="14" t="n">
         <v>2101.21</v>
       </c>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n">
+      <c r="H44" s="14" t="n"/>
+      <c r="I44" s="14" t="n"/>
+      <c r="J44" s="14" t="n"/>
+      <c r="K44" s="14" t="n">
         <v>106.21</v>
       </c>
-      <c r="L10" s="5" t="n">
+      <c r="L44" s="14" t="n">
         <v>523.61</v>
       </c>
-      <c r="M10" s="5" t="n">
+      <c r="M44" s="14" t="n">
         <v>906.87</v>
       </c>
-      <c r="N10" s="5" t="n">
+      <c r="N44" s="14" t="n">
         <v>2484.47</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
         <is>
           <t>HTBT</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B45" s="14" t="n">
         <v>4.442</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C45" s="14" t="n">
         <v>4.365</v>
       </c>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n">
+      <c r="D45" s="14" t="n"/>
+      <c r="E45" s="14" t="n">
         <v>7.504</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F45" s="14" t="n">
         <v>2.317</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G45" s="14" t="n">
         <v>2056.03</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="H45" s="14" t="n">
         <v>5.31</v>
       </c>
-      <c r="I11" s="5" t="n">
+      <c r="I45" s="14" t="n">
         <v>16.61</v>
       </c>
-      <c r="J11" s="5" t="n">
+      <c r="J45" s="14" t="n">
         <v>7.5</v>
       </c>
-      <c r="K11" s="5" t="n">
+      <c r="K45" s="14" t="n">
         <v>111.77</v>
       </c>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n">
+      <c r="L45" s="14" t="n"/>
+      <c r="M45" s="14" t="n"/>
+      <c r="N45" s="14" t="n">
         <v>2439.21</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="13" t="inlineStr">
         <is>
           <t>HTAT</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B46" s="14" t="n">
         <v>4.446</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C46" s="14" t="n">
         <v>4.369</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D46" s="14" t="n">
         <v>-0.092</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E46" s="14" t="n">
         <v>7.502</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F46" s="14" t="n">
         <v>2.318</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G46" s="14" t="n">
         <v>2054.67</v>
       </c>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="n">
+      <c r="H46" s="14" t="n"/>
+      <c r="I46" s="14" t="n"/>
+      <c r="J46" s="14" t="n"/>
+      <c r="K46" s="14" t="n">
         <v>110.09</v>
       </c>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n">
+      <c r="L46" s="14" t="n"/>
+      <c r="M46" s="14" t="n"/>
+      <c r="N46" s="14" t="n">
         <v>2437.93</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="13" t="inlineStr">
         <is>
           <t>LTBT</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B47" s="14" t="n">
         <v>4.487</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C47" s="14" t="n">
         <v>4.397</v>
       </c>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n">
+      <c r="D47" s="14" t="n"/>
+      <c r="E47" s="14" t="n">
         <v>6.346</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F47" s="14" t="n">
         <v>2.317</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G47" s="14" t="n">
         <v>2240.03</v>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="H47" s="14" t="n">
         <v>4.907</v>
       </c>
-      <c r="I13" s="5" t="n">
+      <c r="I47" s="14" t="n">
         <v>16.2</v>
       </c>
-      <c r="J13" s="5" t="n">
+      <c r="J47" s="14" t="n">
         <v>7.43</v>
       </c>
-      <c r="K13" s="5" t="n">
+      <c r="K47" s="14" t="n">
         <v>118.6</v>
       </c>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n">
+      <c r="L47" s="14" t="n"/>
+      <c r="M47" s="14" t="n"/>
+      <c r="N47" s="14" t="n">
         <v>2623.21</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
         <is>
           <t>LTAT</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B48" s="14" t="n">
         <v>4.496</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C48" s="14" t="n">
         <v>4.406</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D48" s="14" t="n">
         <v>-0.205</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E48" s="14" t="n">
         <v>6.343</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F48" s="14" t="n">
         <v>2.318</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="G48" s="14" t="n">
         <v>2239.94</v>
       </c>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n">
+      <c r="H48" s="14" t="n"/>
+      <c r="I48" s="14" t="n"/>
+      <c r="J48" s="14" t="n"/>
+      <c r="K48" s="14" t="n">
         <v>118.58</v>
       </c>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n">
+      <c r="L48" s="14" t="n"/>
+      <c r="M48" s="14" t="n"/>
+      <c r="N48" s="14" t="n">
         <v>2623.2</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="n"/>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="n"/>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="5" t="n"/>
+    <row r="50">
+      <c r="A50" s="8" t="n"/>
+      <c r="B50" s="9" t="n"/>
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="9" t="n"/>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="9" t="n"/>
+      <c r="G50" s="9" t="n"/>
+      <c r="H50" s="9" t="n"/>
+      <c r="I50" s="9" t="n"/>
+      <c r="J50" s="9" t="n"/>
+      <c r="K50" s="9" t="n"/>
+      <c r="L50" s="9" t="n"/>
+      <c r="M50" s="9" t="n"/>
+      <c r="N50" s="9" t="n"/>
+      <c r="O50" s="9" t="n"/>
+      <c r="P50" s="10" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>TEST ENGINEER</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
+  <mergeCells count="19">
+    <mergeCell ref="A4:P4"/>
+    <mergeCell ref="F7:P7"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="A41:N41"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A51:P51"/>
+    <mergeCell ref="F8:P8"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="M6:P6"/>
+    <mergeCell ref="A50:P50"/>
+    <mergeCell ref="A3:P3"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A2:P2"/>
+  </mergeCells>
+  <dataValidations count="38">
+    <dataValidation sqref="B11:B12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (V)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="C11:C12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (I)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="D11:D12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (P)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="E11:E12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (f)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="A16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (V (50%))" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (I (50%))" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="C16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (P (50%))" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="D16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (f (50%))" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="B20:B21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (LVR1)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="C20:C21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (LVR2)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="D20:D21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (LVR3)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="E20:E21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (Temp)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="B25:B30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (V1)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="C25:C30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (V2)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="D25:D30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (V3)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="E25:E30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (I1)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="F25:F30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (I2)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="G25:G30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (I3)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="H25:H30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (P1)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="I25:I30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (P2)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="J25:J30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (P3)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="K25:K30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (f )" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="B34:B39" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (HVR1)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="C34:C39" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (HVR2)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="D34:D39" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (HVR3)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="B43:B48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (%Z-75deg)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="C43:C48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (%X-50Hz)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="D43:D48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (%X Change)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="E43:E48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (Rhv-Ohm)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="F43:F48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (Rlv-mOhm)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="G43:G48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (100% LoadLoss)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="H43:H48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (X/R-75deg)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="I43:I48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (Isc-pk)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="J43:J48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (Isc-rms)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="K43:K48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (Stray Loss)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="L43:L48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (50% LoadLoss)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="M43:M48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (50% TotalLoss)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="N43:N48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (100% TotalLoss)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>